--- a/sample/class_data.xlsx
+++ b/sample/class_data.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Smart Seating Allocator\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF04CE92-8D90-4508-9629-34195A84A8EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Class Room</t>
   </si>
@@ -68,13 +74,118 @@
   </si>
   <si>
     <t>C012</t>
+  </si>
+  <si>
+    <t>C013</t>
+  </si>
+  <si>
+    <t>C103</t>
+  </si>
+  <si>
+    <t>C106</t>
+  </si>
+  <si>
+    <t>C107</t>
+  </si>
+  <si>
+    <t>C109</t>
+  </si>
+  <si>
+    <t>CX001</t>
+  </si>
+  <si>
+    <t>CX101</t>
+  </si>
+  <si>
+    <t>CX102</t>
+  </si>
+  <si>
+    <t>CX103</t>
+  </si>
+  <si>
+    <t>CX104</t>
+  </si>
+  <si>
+    <t>CX201</t>
+  </si>
+  <si>
+    <t>CX202</t>
+  </si>
+  <si>
+    <t>CX203</t>
+  </si>
+  <si>
+    <t>CX204</t>
+  </si>
+  <si>
+    <t>C-208</t>
+  </si>
+  <si>
+    <t>H501</t>
+  </si>
+  <si>
+    <t>H507</t>
+  </si>
+  <si>
+    <t>H508</t>
+  </si>
+  <si>
+    <t>H509</t>
+  </si>
+  <si>
+    <t>H510</t>
+  </si>
+  <si>
+    <t>H601</t>
+  </si>
+  <si>
+    <t>H607</t>
+  </si>
+  <si>
+    <t>H609</t>
+  </si>
+  <si>
+    <t>H610</t>
+  </si>
+  <si>
+    <t>H701</t>
+  </si>
+  <si>
+    <t>H709</t>
+  </si>
+  <si>
+    <t>H712</t>
+  </si>
+  <si>
+    <t>H-801</t>
+  </si>
+  <si>
+    <t>H-802</t>
+  </si>
+  <si>
+    <t>H-811</t>
+  </si>
+  <si>
+    <t>I-007</t>
+  </si>
+  <si>
+    <t>I-008</t>
+  </si>
+  <si>
+    <t>I-010</t>
+  </si>
+  <si>
+    <t>I-011</t>
+  </si>
+  <si>
+    <t>I-012</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +201,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -99,7 +221,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -122,21 +244,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -183,7 +379,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -215,9 +411,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -249,6 +463,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -424,11 +656,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,132 +668,412 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B2" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B3" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="B4" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="B5" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="B6" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="4">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="4">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="4">
         <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
